--- a/artfynd/A 64950-2023 artfynd.xlsx
+++ b/artfynd/A 64950-2023 artfynd.xlsx
@@ -795,7 +795,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131772604</v>
+        <v>131772607</v>
       </c>
       <c r="B3" t="n">
         <v>57899</v>
@@ -838,10 +838,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>564926</v>
+        <v>564755</v>
       </c>
       <c r="R3" t="n">
-        <v>6913858</v>
+        <v>6913996</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -873,7 +873,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -883,12 +883,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>färska ringhack på gran</t>
+          <t>färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -915,7 +915,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131772607</v>
+        <v>131772604</v>
       </c>
       <c r="B4" t="n">
         <v>57899</v>
@@ -958,10 +958,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>564755</v>
+        <v>564926</v>
       </c>
       <c r="R4" t="n">
-        <v>6913996</v>
+        <v>6913858</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,7 +993,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1003,12 +1003,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>färska och äldre ringhack på tall</t>
+          <t>färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1249,7 +1249,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131772615</v>
+        <v>131772608</v>
       </c>
       <c r="B7" t="n">
         <v>91849</v>
@@ -1280,10 +1280,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>564615</v>
+        <v>564728</v>
       </c>
       <c r="R7" t="n">
-        <v>6913871</v>
+        <v>6913971</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1315,7 +1315,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1325,7 +1325,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1352,10 +1352,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131772608</v>
+        <v>131772609</v>
       </c>
       <c r="B8" t="n">
-        <v>91849</v>
+        <v>91829</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1363,19 +1363,23 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr"/>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1383,10 +1387,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>564728</v>
+        <v>564692</v>
       </c>
       <c r="R8" t="n">
-        <v>6913971</v>
+        <v>6913946</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1418,7 +1422,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1428,7 +1432,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1455,10 +1459,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131772609</v>
+        <v>131772615</v>
       </c>
       <c r="B9" t="n">
-        <v>91829</v>
+        <v>91849</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1466,23 +1470,19 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1490,10 +1490,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>564692</v>
+        <v>564615</v>
       </c>
       <c r="R9" t="n">
-        <v>6913946</v>
+        <v>6913871</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1525,7 +1525,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1535,7 +1535,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1665,10 +1665,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131772616</v>
+        <v>131772612</v>
       </c>
       <c r="B11" t="n">
-        <v>57899</v>
+        <v>91849</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1676,42 +1676,30 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Svartåstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>564592</v>
+        <v>564665</v>
       </c>
       <c r="R11" t="n">
-        <v>6913866</v>
+        <v>6913987</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1743,7 +1731,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1753,12 +1741,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:37</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>färska ringhack på tall</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1785,10 +1768,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131772612</v>
+        <v>131772616</v>
       </c>
       <c r="B12" t="n">
-        <v>91849</v>
+        <v>57899</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1796,30 +1779,42 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Svartåstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>564665</v>
+        <v>564592</v>
       </c>
       <c r="R12" t="n">
-        <v>6913987</v>
+        <v>6913866</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1851,7 +1846,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1861,7 +1856,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:37</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 64950-2023 artfynd.xlsx
+++ b/artfynd/A 64950-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131772606</v>
       </c>
       <c r="B2" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,10 +795,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131772607</v>
+        <v>131772604</v>
       </c>
       <c r="B3" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -838,10 +838,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>564755</v>
+        <v>564926</v>
       </c>
       <c r="R3" t="n">
-        <v>6913996</v>
+        <v>6913858</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -873,7 +873,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -883,12 +883,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>färska och äldre ringhack på tall</t>
+          <t>färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -915,10 +915,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131772604</v>
+        <v>131772607</v>
       </c>
       <c r="B4" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -958,10 +958,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>564926</v>
+        <v>564755</v>
       </c>
       <c r="R4" t="n">
-        <v>6913858</v>
+        <v>6913996</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,7 +993,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1003,12 +1003,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>färska ringhack på gran</t>
+          <t>färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1038,7 +1038,7 @@
         <v>131772613</v>
       </c>
       <c r="B5" t="n">
-        <v>92552</v>
+        <v>92555</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1145,7 +1145,7 @@
         <v>131772603</v>
       </c>
       <c r="B6" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1252,7 +1252,7 @@
         <v>131772608</v>
       </c>
       <c r="B7" t="n">
-        <v>91849</v>
+        <v>91852</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>131772609</v>
       </c>
       <c r="B8" t="n">
-        <v>91829</v>
+        <v>91832</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1462,7 +1462,7 @@
         <v>131772615</v>
       </c>
       <c r="B9" t="n">
-        <v>91849</v>
+        <v>91852</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1565,7 +1565,7 @@
         <v>131772610</v>
       </c>
       <c r="B10" t="n">
-        <v>91849</v>
+        <v>91852</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1668,7 +1668,7 @@
         <v>131772612</v>
       </c>
       <c r="B11" t="n">
-        <v>91849</v>
+        <v>91852</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
         <v>131772616</v>
       </c>
       <c r="B12" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1891,7 +1891,7 @@
         <v>131772614</v>
       </c>
       <c r="B13" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2011,7 +2011,7 @@
         <v>131772611</v>
       </c>
       <c r="B14" t="n">
-        <v>91849</v>
+        <v>91852</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 64950-2023 artfynd.xlsx
+++ b/artfynd/A 64950-2023 artfynd.xlsx
@@ -795,7 +795,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131772604</v>
+        <v>131772607</v>
       </c>
       <c r="B3" t="n">
         <v>57902</v>
@@ -838,10 +838,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>564926</v>
+        <v>564755</v>
       </c>
       <c r="R3" t="n">
-        <v>6913858</v>
+        <v>6913996</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -873,7 +873,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -883,12 +883,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>färska ringhack på gran</t>
+          <t>färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -915,7 +915,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131772607</v>
+        <v>131772604</v>
       </c>
       <c r="B4" t="n">
         <v>57902</v>
@@ -958,10 +958,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>564755</v>
+        <v>564926</v>
       </c>
       <c r="R4" t="n">
-        <v>6913996</v>
+        <v>6913858</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,7 +993,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1003,12 +1003,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>färska och äldre ringhack på tall</t>
+          <t>färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1352,10 +1352,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131772609</v>
+        <v>131772615</v>
       </c>
       <c r="B8" t="n">
-        <v>91832</v>
+        <v>91852</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1363,23 +1363,19 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1387,10 +1383,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>564692</v>
+        <v>564615</v>
       </c>
       <c r="R8" t="n">
-        <v>6913946</v>
+        <v>6913871</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1422,7 +1418,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1432,7 +1428,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1459,10 +1455,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131772615</v>
+        <v>131772609</v>
       </c>
       <c r="B9" t="n">
-        <v>91852</v>
+        <v>91832</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1470,19 +1466,23 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr"/>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1490,10 +1490,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>564615</v>
+        <v>564692</v>
       </c>
       <c r="R9" t="n">
-        <v>6913871</v>
+        <v>6913946</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1525,7 +1525,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1535,7 +1535,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1665,10 +1665,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131772612</v>
+        <v>131772616</v>
       </c>
       <c r="B11" t="n">
-        <v>91852</v>
+        <v>57902</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1676,30 +1676,42 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Svartåstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>564665</v>
+        <v>564592</v>
       </c>
       <c r="R11" t="n">
-        <v>6913987</v>
+        <v>6913866</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1731,7 +1743,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1741,7 +1753,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:37</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1768,10 +1785,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131772616</v>
+        <v>131772612</v>
       </c>
       <c r="B12" t="n">
-        <v>57902</v>
+        <v>91852</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1779,42 +1796,30 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Svartåstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>564592</v>
+        <v>564665</v>
       </c>
       <c r="R12" t="n">
-        <v>6913866</v>
+        <v>6913987</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1846,7 +1851,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1856,12 +1861,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:37</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>färska ringhack på tall</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 64950-2023 artfynd.xlsx
+++ b/artfynd/A 64950-2023 artfynd.xlsx
@@ -1249,10 +1249,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131772608</v>
+        <v>131772609</v>
       </c>
       <c r="B7" t="n">
-        <v>91852</v>
+        <v>91832</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,19 +1260,23 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr"/>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1280,10 +1284,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>564728</v>
+        <v>564692</v>
       </c>
       <c r="R7" t="n">
-        <v>6913971</v>
+        <v>6913946</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1315,7 +1319,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1325,7 +1329,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1455,10 +1459,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131772609</v>
+        <v>131772608</v>
       </c>
       <c r="B9" t="n">
-        <v>91832</v>
+        <v>91852</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1466,23 +1470,19 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1490,10 +1490,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>564692</v>
+        <v>564728</v>
       </c>
       <c r="R9" t="n">
-        <v>6913946</v>
+        <v>6913971</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1525,7 +1525,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1535,7 +1535,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1665,10 +1665,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131772616</v>
+        <v>131772612</v>
       </c>
       <c r="B11" t="n">
-        <v>57902</v>
+        <v>91852</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1676,42 +1676,30 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Svartåstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>564592</v>
+        <v>564665</v>
       </c>
       <c r="R11" t="n">
-        <v>6913866</v>
+        <v>6913987</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1743,7 +1731,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1753,12 +1741,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:37</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>färska ringhack på tall</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1785,10 +1768,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131772612</v>
+        <v>131772616</v>
       </c>
       <c r="B12" t="n">
-        <v>91852</v>
+        <v>57902</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1796,30 +1779,42 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Svartåstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>564665</v>
+        <v>564592</v>
       </c>
       <c r="R12" t="n">
-        <v>6913987</v>
+        <v>6913866</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1851,7 +1846,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1861,7 +1856,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:37</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 64950-2023 artfynd.xlsx
+++ b/artfynd/A 64950-2023 artfynd.xlsx
@@ -1665,10 +1665,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131772612</v>
+        <v>131772616</v>
       </c>
       <c r="B11" t="n">
-        <v>91852</v>
+        <v>57902</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1676,30 +1676,42 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Svartåstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>564665</v>
+        <v>564592</v>
       </c>
       <c r="R11" t="n">
-        <v>6913987</v>
+        <v>6913866</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1731,7 +1743,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1741,7 +1753,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:37</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1768,10 +1785,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131772616</v>
+        <v>131772612</v>
       </c>
       <c r="B12" t="n">
-        <v>57902</v>
+        <v>91852</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1779,42 +1796,30 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Svartåstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>564592</v>
+        <v>564665</v>
       </c>
       <c r="R12" t="n">
-        <v>6913866</v>
+        <v>6913987</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1846,7 +1851,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1856,12 +1861,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:37</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>färska ringhack på tall</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 64950-2023 artfynd.xlsx
+++ b/artfynd/A 64950-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131772606</v>
       </c>
       <c r="B2" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>131772607</v>
       </c>
       <c r="B3" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -918,7 +918,7 @@
         <v>131772604</v>
       </c>
       <c r="B4" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1038,7 +1038,7 @@
         <v>131772613</v>
       </c>
       <c r="B5" t="n">
-        <v>92555</v>
+        <v>92561</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1145,7 +1145,7 @@
         <v>131772603</v>
       </c>
       <c r="B6" t="n">
-        <v>79264</v>
+        <v>79266</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1252,7 +1252,7 @@
         <v>131772609</v>
       </c>
       <c r="B7" t="n">
-        <v>91832</v>
+        <v>91838</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1356,10 +1356,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131772615</v>
+        <v>131772608</v>
       </c>
       <c r="B8" t="n">
-        <v>91852</v>
+        <v>91858</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1387,10 +1387,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>564615</v>
+        <v>564728</v>
       </c>
       <c r="R8" t="n">
-        <v>6913871</v>
+        <v>6913971</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1422,7 +1422,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1459,10 +1459,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131772608</v>
+        <v>131772615</v>
       </c>
       <c r="B9" t="n">
-        <v>91852</v>
+        <v>91858</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1490,10 +1490,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>564728</v>
+        <v>564615</v>
       </c>
       <c r="R9" t="n">
-        <v>6913971</v>
+        <v>6913871</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1525,7 +1525,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1535,7 +1535,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1565,7 +1565,7 @@
         <v>131772610</v>
       </c>
       <c r="B10" t="n">
-        <v>91852</v>
+        <v>91858</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1665,10 +1665,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131772616</v>
+        <v>131772612</v>
       </c>
       <c r="B11" t="n">
-        <v>57902</v>
+        <v>91858</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1676,42 +1676,30 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Svartåstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>564592</v>
+        <v>564665</v>
       </c>
       <c r="R11" t="n">
-        <v>6913866</v>
+        <v>6913987</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1743,7 +1731,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1753,12 +1741,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:37</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>färska ringhack på tall</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1785,10 +1768,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131772612</v>
+        <v>131772616</v>
       </c>
       <c r="B12" t="n">
-        <v>91852</v>
+        <v>57904</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1796,30 +1779,42 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Svartåstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>564665</v>
+        <v>564592</v>
       </c>
       <c r="R12" t="n">
-        <v>6913987</v>
+        <v>6913866</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1851,7 +1846,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1861,7 +1856,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:37</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1891,7 +1891,7 @@
         <v>131772614</v>
       </c>
       <c r="B13" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2011,7 +2011,7 @@
         <v>131772611</v>
       </c>
       <c r="B14" t="n">
-        <v>91852</v>
+        <v>91858</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 64950-2023 artfynd.xlsx
+++ b/artfynd/A 64950-2023 artfynd.xlsx
@@ -1038,7 +1038,7 @@
         <v>131772613</v>
       </c>
       <c r="B5" t="n">
-        <v>92612</v>
+        <v>92615</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1145,7 +1145,7 @@
         <v>131772603</v>
       </c>
       <c r="B6" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1249,10 +1249,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131772609</v>
+        <v>131772608</v>
       </c>
       <c r="B7" t="n">
-        <v>91889</v>
+        <v>91912</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,23 +1260,19 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1284,10 +1280,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>564692</v>
+        <v>564728</v>
       </c>
       <c r="R7" t="n">
-        <v>6913946</v>
+        <v>6913971</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1319,7 +1315,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1329,7 +1325,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1356,10 +1352,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131772608</v>
+        <v>131772615</v>
       </c>
       <c r="B8" t="n">
-        <v>91909</v>
+        <v>91912</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1387,10 +1383,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>564728</v>
+        <v>564615</v>
       </c>
       <c r="R8" t="n">
-        <v>6913971</v>
+        <v>6913871</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1422,7 +1418,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1432,7 +1428,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1459,10 +1455,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131772615</v>
+        <v>131772609</v>
       </c>
       <c r="B9" t="n">
-        <v>91909</v>
+        <v>91892</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1470,19 +1466,23 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr"/>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1490,10 +1490,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>564615</v>
+        <v>564692</v>
       </c>
       <c r="R9" t="n">
-        <v>6913871</v>
+        <v>6913946</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1525,7 +1525,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1535,7 +1535,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1565,7 +1565,7 @@
         <v>131772610</v>
       </c>
       <c r="B10" t="n">
-        <v>91909</v>
+        <v>91912</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1668,7 +1668,7 @@
         <v>131772612</v>
       </c>
       <c r="B11" t="n">
-        <v>91909</v>
+        <v>91912</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2011,7 +2011,7 @@
         <v>131772611</v>
       </c>
       <c r="B14" t="n">
-        <v>91909</v>
+        <v>91912</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 64950-2023 artfynd.xlsx
+++ b/artfynd/A 64950-2023 artfynd.xlsx
@@ -1249,10 +1249,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131772608</v>
+        <v>131772609</v>
       </c>
       <c r="B7" t="n">
-        <v>91912</v>
+        <v>91892</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,19 +1260,23 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr"/>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1280,10 +1284,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>564728</v>
+        <v>564692</v>
       </c>
       <c r="R7" t="n">
-        <v>6913971</v>
+        <v>6913946</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1315,7 +1319,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1325,7 +1329,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1352,7 +1356,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131772615</v>
+        <v>131772608</v>
       </c>
       <c r="B8" t="n">
         <v>91912</v>
@@ -1383,10 +1387,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>564615</v>
+        <v>564728</v>
       </c>
       <c r="R8" t="n">
-        <v>6913871</v>
+        <v>6913971</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1418,7 +1422,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1428,7 +1432,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1455,10 +1459,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131772609</v>
+        <v>131772615</v>
       </c>
       <c r="B9" t="n">
-        <v>91892</v>
+        <v>91912</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1466,23 +1470,19 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1490,10 +1490,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>564692</v>
+        <v>564615</v>
       </c>
       <c r="R9" t="n">
-        <v>6913946</v>
+        <v>6913871</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1525,7 +1525,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1535,7 +1535,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1665,10 +1665,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131772612</v>
+        <v>131772616</v>
       </c>
       <c r="B11" t="n">
-        <v>91912</v>
+        <v>57948</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1676,30 +1676,42 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Svartåstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>564665</v>
+        <v>564592</v>
       </c>
       <c r="R11" t="n">
-        <v>6913987</v>
+        <v>6913866</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1731,7 +1743,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1741,7 +1753,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:37</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1768,10 +1785,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131772616</v>
+        <v>131772612</v>
       </c>
       <c r="B12" t="n">
-        <v>57948</v>
+        <v>91912</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1779,42 +1796,30 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Svartåstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>564592</v>
+        <v>564665</v>
       </c>
       <c r="R12" t="n">
-        <v>6913866</v>
+        <v>6913987</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1846,7 +1851,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1856,12 +1861,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:37</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>färska ringhack på tall</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 64950-2023 artfynd.xlsx
+++ b/artfynd/A 64950-2023 artfynd.xlsx
@@ -1665,10 +1665,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131772616</v>
+        <v>131772612</v>
       </c>
       <c r="B11" t="n">
-        <v>57948</v>
+        <v>91912</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1676,42 +1676,30 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Svartåstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>564592</v>
+        <v>564665</v>
       </c>
       <c r="R11" t="n">
-        <v>6913866</v>
+        <v>6913987</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1743,7 +1731,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1753,12 +1741,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:37</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>färska ringhack på tall</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1785,10 +1768,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131772612</v>
+        <v>131772616</v>
       </c>
       <c r="B12" t="n">
-        <v>91912</v>
+        <v>57948</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1796,30 +1779,42 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Svartåstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>564665</v>
+        <v>564592</v>
       </c>
       <c r="R12" t="n">
-        <v>6913987</v>
+        <v>6913866</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1851,7 +1846,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1861,7 +1856,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:37</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD12" t="b">
